--- a/Albert_Project/outputs/23-033/23-033_Cabinet_Estimation_NEW.xlsx
+++ b/Albert_Project/outputs/23-033/23-033_Cabinet_Estimation_NEW.xlsx
@@ -2885,7 +2885,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>1</v>
@@ -2927,7 +2927,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="17" t="n">
         <v>1</v>
@@ -2969,7 +2969,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>1</v>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>base 35.4"W × 28.3"H</t>
+          <t>base 35.4"W × 28.4"H</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -3008,10 +3008,10 @@
         <v>35.4</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>1</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>base 30.0"W × 28.3"H</t>
+          <t>base 30.0"W × 28.4"H</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
@@ -3050,10 +3050,10 @@
         <v>30</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>1</v>
@@ -3095,7 +3095,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>1</v>
@@ -3137,7 +3137,7 @@
         <v>30</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="17" t="n">
         <v>1</v>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>vanity 74.0"W × 34.3"H</t>
+          <t>vanity 74.0"W × 34.2"H</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
@@ -3255,10 +3255,10 @@
         <v>74</v>
       </c>
       <c r="F23" s="17" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>20.9</v>
+        <v>0.8</v>
       </c>
       <c r="H23" s="17" t="n">
         <v>1</v>
@@ -3300,7 +3300,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="G24" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H24" s="17" t="n">
         <v>1</v>
@@ -3566,7 +3566,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>1</v>
@@ -3608,7 +3608,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="17" t="n">
         <v>1</v>
@@ -3650,7 +3650,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>1</v>
@@ -3692,7 +3692,7 @@
         <v>34</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>1</v>
@@ -3734,7 +3734,7 @@
         <v>34</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>1</v>
@@ -3776,7 +3776,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>1</v>
@@ -3818,7 +3818,7 @@
         <v>30</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="17" t="n">
         <v>1</v>
@@ -3939,7 +3939,7 @@
         <v>34</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>20.9</v>
+        <v>0.8</v>
       </c>
       <c r="H23" s="17" t="n">
         <v>1</v>
@@ -3981,7 +3981,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="G24" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H24" s="17" t="n">
         <v>1</v>
@@ -4247,7 +4247,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>1</v>
@@ -4289,7 +4289,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="17" t="n">
         <v>1</v>
@@ -4331,7 +4331,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>1</v>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>base 35.4"W × 28.3"H</t>
+          <t>base 35.4"W × 28.4"H</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -4370,10 +4370,10 @@
         <v>35.4</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>1</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>base 30.0"W × 28.3"H</t>
+          <t>base 30.0"W × 28.4"H</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
@@ -4412,10 +4412,10 @@
         <v>30</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>1</v>
@@ -4457,7 +4457,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>1</v>
@@ -4499,7 +4499,7 @@
         <v>30</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="17" t="n">
         <v>1</v>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>vanity 74.0"W × 34.3"H</t>
+          <t>vanity 74.0"W × 34.2"H</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
@@ -4617,10 +4617,10 @@
         <v>74</v>
       </c>
       <c r="F23" s="17" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>20.9</v>
+        <v>0.8</v>
       </c>
       <c r="H23" s="17" t="n">
         <v>1</v>
@@ -4662,7 +4662,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="G24" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H24" s="17" t="n">
         <v>1</v>
@@ -4928,7 +4928,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>1</v>
@@ -4970,7 +4970,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="17" t="n">
         <v>1</v>
@@ -5012,7 +5012,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>1</v>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>base 35.4"W × 28.3"H</t>
+          <t>base 35.4"W × 28.4"H</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -5051,10 +5051,10 @@
         <v>35.4</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>1</v>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>base 30.0"W × 28.3"H</t>
+          <t>base 30.0"W × 28.4"H</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
@@ -5093,10 +5093,10 @@
         <v>30</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>1</v>
@@ -5138,7 +5138,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>1</v>
@@ -5180,7 +5180,7 @@
         <v>30</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="17" t="n">
         <v>1</v>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>vanity 74.0"W × 34.3"H</t>
+          <t>vanity 74.0"W × 34.2"H</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
@@ -5298,10 +5298,10 @@
         <v>74</v>
       </c>
       <c r="F23" s="17" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>20.9</v>
+        <v>0.8</v>
       </c>
       <c r="H23" s="17" t="n">
         <v>1</v>
@@ -5343,7 +5343,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="G24" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H24" s="17" t="n">
         <v>1</v>
@@ -5609,7 +5609,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>1</v>
@@ -5651,7 +5651,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="17" t="n">
         <v>1</v>
@@ -5693,7 +5693,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>1</v>
@@ -5735,7 +5735,7 @@
         <v>34</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>1</v>
@@ -5777,7 +5777,7 @@
         <v>34</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>1</v>
@@ -5819,7 +5819,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>1</v>
@@ -5861,7 +5861,7 @@
         <v>30</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>13</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="17" t="n">
         <v>1</v>
@@ -5982,7 +5982,7 @@
         <v>34</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>20.9</v>
+        <v>0.8</v>
       </c>
       <c r="H23" s="17" t="n">
         <v>1</v>
@@ -6024,7 +6024,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="G24" s="17" t="n">
-        <v>23.6</v>
+        <v>0.9</v>
       </c>
       <c r="H24" s="17" t="n">
         <v>1</v>
